--- a/pages/CNT Data.xlsx
+++ b/pages/CNT Data.xlsx
@@ -3033,19 +3033,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3058,6 +3052,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3365,64 +3365,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="25" t="s">
+      <c r="J1" s="23" t="s">
         <v>348</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="26" t="s">
+      <c r="K1" s="23"/>
+      <c r="L1" s="24" t="s">
         <v>349</v>
       </c>
-      <c r="M1" s="26"/>
-      <c r="N1" s="27" t="s">
+      <c r="M1" s="24"/>
+      <c r="N1" s="25" t="s">
         <v>855</v>
       </c>
-      <c r="O1" s="27"/>
-      <c r="P1" s="22" t="s">
+      <c r="O1" s="25"/>
+      <c r="P1" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="23" t="s">
+      <c r="Q1" s="19"/>
+      <c r="R1" s="20" t="s">
         <v>584</v>
       </c>
-      <c r="S1" s="23"/>
+      <c r="S1" s="20"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="20"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="24"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="22"/>
       <c r="J2" s="10" t="s">
         <v>351</v>
       </c>
@@ -12618,7 +12618,7 @@
         <v>696</v>
       </c>
       <c r="Q229" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="230" spans="1:19">
@@ -12651,7 +12651,7 @@
         <v>871</v>
       </c>
       <c r="Q230" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="231" spans="1:19">
@@ -12684,7 +12684,7 @@
         <v>872</v>
       </c>
       <c r="Q231" s="2">
-        <v>225.75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="232" spans="1:19">
@@ -12717,7 +12717,7 @@
         <v>697</v>
       </c>
       <c r="Q232" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="233" spans="1:19">
@@ -12750,7 +12750,7 @@
         <v>869</v>
       </c>
       <c r="Q233" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="234" spans="1:19">
@@ -12783,7 +12783,7 @@
         <v>874</v>
       </c>
       <c r="Q234" s="2">
-        <v>225.75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="235" spans="1:19">
@@ -12816,7 +12816,7 @@
         <v>698</v>
       </c>
       <c r="Q235" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="236" spans="1:19">
@@ -12849,7 +12849,7 @@
         <v>936</v>
       </c>
       <c r="Q236" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="237" spans="1:19">
@@ -12882,7 +12882,7 @@
         <v>873</v>
       </c>
       <c r="Q237" s="2">
-        <v>225.75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="238" spans="1:19">
@@ -12915,7 +12915,7 @@
         <v>699</v>
       </c>
       <c r="Q238" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="239" spans="1:19">
@@ -12948,7 +12948,7 @@
         <v>937</v>
       </c>
       <c r="Q239" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="240" spans="1:19">
@@ -12981,7 +12981,7 @@
         <v>924</v>
       </c>
       <c r="Q240" s="2">
-        <v>225.75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="241" spans="1:17">
@@ -13014,7 +13014,7 @@
         <v>700</v>
       </c>
       <c r="Q241" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="242" spans="1:17">
@@ -13047,7 +13047,7 @@
         <v>938</v>
       </c>
       <c r="Q242" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="243" spans="1:17">
@@ -13080,7 +13080,7 @@
         <v>925</v>
       </c>
       <c r="Q243" s="2">
-        <v>225.75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="244" spans="1:17">
@@ -13113,7 +13113,7 @@
         <v>701</v>
       </c>
       <c r="Q244" s="2">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="245" spans="1:17">
@@ -13146,7 +13146,7 @@
         <v>939</v>
       </c>
       <c r="Q245" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="246" spans="1:17">
@@ -13179,7 +13179,7 @@
         <v>926</v>
       </c>
       <c r="Q246" s="2">
-        <v>225.75</v>
+        <v>215</v>
       </c>
     </row>
     <row r="247" spans="1:17">
@@ -16818,6 +16818,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:S1"/>
     <mergeCell ref="G1:G2"/>
@@ -16826,12 +16832,6 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
